--- a/output/yearly_benthic_cover_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_5_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.47195579794597</v>
+        <v>45.66402506540302</v>
       </c>
       <c r="M2" t="n">
-        <v>98.79550318826904</v>
+        <v>100.0080775785875</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00156216629925</v>
+        <v>88.03022919926327</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89151765051292</v>
+        <v>45.90414122156643</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228692746727859</v>
+        <v>2.228756720127899</v>
       </c>
       <c r="E3" t="n">
-        <v>5.683808720251205</v>
+        <v>5.692588119665906</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428975822426196</v>
+        <v>0.7429189067092996</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9604728357915</v>
+        <v>33.96455426569118</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1732887831605</v>
+        <v>34.17426970862778</v>
       </c>
       <c r="I3" t="n">
-        <v>6.569291609109206</v>
+        <v>6.583898311508092</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643109889016372</v>
+        <v>4.643243166933122</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99843783370073</v>
+        <v>11.96977080073672</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87423662818035</v>
+        <v>48.88976255906147</v>
       </c>
       <c r="M3" t="n">
-        <v>106.764192112394</v>
+        <v>106.7636745813646</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.1529255315648</v>
+        <v>87.19803503251867</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67963686265496</v>
+        <v>42.71105416649245</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18810543034464</v>
+        <v>2.189066779978835</v>
       </c>
       <c r="E4" t="n">
-        <v>6.494615370165442</v>
+        <v>6.507566141939136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444563208468411</v>
+        <v>0.7444803533824953</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34200963240301</v>
+        <v>33.35970981864109</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24499075895469</v>
+        <v>34.24609625559479</v>
       </c>
       <c r="I4" t="n">
-        <v>5.485896013557404</v>
+        <v>5.498113474341737</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652852005292757</v>
+        <v>4.653002208640595</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84707446843522</v>
+        <v>12.80196496748134</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29080834643455</v>
+        <v>44.30409480181765</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81751967752473</v>
+        <v>99.81711393579144</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12180870076041</v>
+        <v>86.03876416945707</v>
       </c>
       <c r="C5" t="n">
-        <v>42.49999992483853</v>
+        <v>42.4051791023163</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138201562591198</v>
+        <v>2.13251116058632</v>
       </c>
       <c r="E5" t="n">
-        <v>7.1097739966405</v>
+        <v>7.104424740477512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457759146934148</v>
+        <v>0.7458042127921837</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58158227078938</v>
+        <v>32.49784527033067</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30569207589708</v>
+        <v>34.30699378844045</v>
       </c>
       <c r="I5" t="n">
-        <v>4.579683413314983</v>
+        <v>4.589908666878766</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661099466833842</v>
+        <v>4.661276329951148</v>
       </c>
       <c r="K5" t="n">
-        <v>13.8781912992396</v>
+        <v>13.96123583054294</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46942277554528</v>
+        <v>43.48085969285349</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84761399962342</v>
+        <v>99.84727462571274</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.94749824242029</v>
+        <v>84.74912441558224</v>
       </c>
       <c r="C6" t="n">
-        <v>42.03709042711255</v>
+        <v>41.82843294515614</v>
       </c>
       <c r="D6" t="n">
-        <v>2.081291178355552</v>
+        <v>2.069728497585069</v>
       </c>
       <c r="E6" t="n">
-        <v>7.557561327860824</v>
+        <v>7.533713166527387</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468944291023895</v>
+        <v>0.7469278988807972</v>
       </c>
       <c r="G6" t="n">
-        <v>31.71439070266198</v>
+        <v>31.54108532197334</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35714373870992</v>
+        <v>34.35868334851667</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822126683839683</v>
+        <v>3.830686814093988</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668090181889934</v>
+        <v>4.668299368004983</v>
       </c>
       <c r="K6" t="n">
-        <v>15.05250175757974</v>
+        <v>15.25087558441776</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78319438716008</v>
+        <v>42.79319400745724</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87278657185237</v>
+        <v>99.87250253703114</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.71752288877447</v>
+        <v>83.22519068188669</v>
       </c>
       <c r="C7" t="n">
-        <v>41.40101321264601</v>
+        <v>40.89956098656187</v>
       </c>
       <c r="D7" t="n">
-        <v>2.021951270367507</v>
+        <v>1.995620259283765</v>
       </c>
       <c r="E7" t="n">
-        <v>7.87361192133412</v>
+        <v>7.796683656512167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478428400255979</v>
+        <v>0.747884109699375</v>
       </c>
       <c r="G7" t="n">
-        <v>30.81017843012459</v>
+        <v>30.41173223530044</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40077064117751</v>
+        <v>34.40266904617125</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189150035585157</v>
+        <v>3.196325689298594</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674017750159987</v>
+        <v>4.674275685621095</v>
       </c>
       <c r="K7" t="n">
-        <v>16.28247711122554</v>
+        <v>16.77480931811331</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21033949046625</v>
+        <v>42.21922172826664</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89382981433781</v>
+        <v>99.89359203294183</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.74977479025448</v>
+        <v>87.96399024320075</v>
       </c>
       <c r="C8" t="n">
-        <v>43.76013735117672</v>
+        <v>43.16322386523338</v>
       </c>
       <c r="D8" t="n">
-        <v>2.026307593476414</v>
+        <v>1.99981794518191</v>
       </c>
       <c r="E8" t="n">
-        <v>9.750278436901699</v>
+        <v>9.598766543551612</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494540781862694</v>
+        <v>0.7494572459541946</v>
       </c>
       <c r="G8" t="n">
-        <v>31.32837908826594</v>
+        <v>30.90597378055756</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4748875965684</v>
+        <v>34.47503331389295</v>
       </c>
       <c r="I8" t="n">
-        <v>5.736380008191559</v>
+        <v>5.550833626848803</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684087988664183</v>
+        <v>4.684107787213717</v>
       </c>
       <c r="K8" t="n">
-        <v>11.25022520974554</v>
+        <v>12.03600975679925</v>
       </c>
       <c r="L8" t="n">
-        <v>44.79883585689258</v>
+        <v>44.61612697002624</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80919841781484</v>
+        <v>99.81536059205888</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.09467522157232</v>
+        <v>85.91023841963994</v>
       </c>
       <c r="C9" t="n">
-        <v>42.99603907373034</v>
+        <v>41.97121280652458</v>
       </c>
       <c r="D9" t="n">
-        <v>1.952074959186239</v>
+        <v>1.906611907246875</v>
       </c>
       <c r="E9" t="n">
-        <v>10.19126224678282</v>
+        <v>9.923729606495868</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508277536034099</v>
+        <v>0.7508047739941031</v>
       </c>
       <c r="G9" t="n">
-        <v>30.18068161368197</v>
+        <v>29.46553097847649</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53807666575687</v>
+        <v>34.53701960372874</v>
       </c>
       <c r="I9" t="n">
-        <v>4.789078522539695</v>
+        <v>4.634011712234703</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692673460021312</v>
+        <v>4.692529837463145</v>
       </c>
       <c r="K9" t="n">
-        <v>12.90532477842768</v>
+        <v>14.08976158036006</v>
       </c>
       <c r="L9" t="n">
-        <v>43.93929225872555</v>
+        <v>43.78483579014734</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84065611088357</v>
+        <v>99.84581017703198</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.16749171191238</v>
+        <v>83.63060486955966</v>
       </c>
       <c r="C10" t="n">
-        <v>41.81281285839168</v>
+        <v>40.41065645394345</v>
       </c>
       <c r="D10" t="n">
-        <v>1.866103920388927</v>
+        <v>1.80413914364437</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4086207747228</v>
+        <v>10.03497373560852</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520023666154575</v>
+        <v>0.7519621790793874</v>
       </c>
       <c r="G10" t="n">
-        <v>28.85149876763961</v>
+        <v>27.8818765499569</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59210886431106</v>
+        <v>34.59026023765183</v>
       </c>
       <c r="I10" t="n">
-        <v>3.997142226887923</v>
+        <v>3.8676294043725</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700014791346609</v>
+        <v>4.699763619246173</v>
       </c>
       <c r="K10" t="n">
-        <v>14.83250828808762</v>
+        <v>16.36939513044033</v>
       </c>
       <c r="L10" t="n">
-        <v>43.22164889456126</v>
+        <v>43.09122586805415</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86697004104056</v>
+        <v>99.87127745243791</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83.14769532691948</v>
+        <v>81.25483123154436</v>
       </c>
       <c r="C11" t="n">
-        <v>40.4135880869972</v>
+        <v>38.63434872088116</v>
       </c>
       <c r="D11" t="n">
-        <v>1.776828281579055</v>
+        <v>1.698476503990961</v>
       </c>
       <c r="E11" t="n">
-        <v>10.46656647955909</v>
+        <v>9.985139460525225</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530078998221358</v>
+        <v>0.7529577306378904</v>
       </c>
       <c r="G11" t="n">
-        <v>27.47122409217222</v>
+        <v>26.24892452120824</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63836339181826</v>
+        <v>34.63605560934296</v>
       </c>
       <c r="I11" t="n">
-        <v>3.335405808080362</v>
+        <v>3.227291589352268</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706299373888348</v>
+        <v>4.705985816486817</v>
       </c>
       <c r="K11" t="n">
-        <v>16.85230467308054</v>
+        <v>18.74516876845564</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6230755113976</v>
+        <v>42.51304836054175</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88896827147533</v>
+        <v>99.89256584987855</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.8997775903424</v>
+        <v>78.81142674933471</v>
       </c>
       <c r="C12" t="n">
-        <v>38.68295982323328</v>
+        <v>36.69032867711827</v>
       </c>
       <c r="D12" t="n">
-        <v>1.678178582815365</v>
+        <v>1.590879645801642</v>
       </c>
       <c r="E12" t="n">
-        <v>10.34924352544691</v>
+        <v>9.801335833601637</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538712680128533</v>
+        <v>0.7538151857576139</v>
       </c>
       <c r="G12" t="n">
-        <v>25.94601875327801</v>
+        <v>24.58608031777404</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67807832859127</v>
+        <v>34.67549854485024</v>
       </c>
       <c r="I12" t="n">
-        <v>2.782691707117668</v>
+        <v>2.692472310564457</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711695425080332</v>
+        <v>4.711344910985089</v>
       </c>
       <c r="K12" t="n">
-        <v>19.1002224096576</v>
+        <v>21.18857325066528</v>
       </c>
       <c r="L12" t="n">
-        <v>42.12416760577358</v>
+        <v>42.03145108362333</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90734983866446</v>
+        <v>99.9103530114069</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.48252155088686</v>
+        <v>76.36121214279046</v>
       </c>
       <c r="C13" t="n">
-        <v>36.69654104941949</v>
+        <v>34.65585086396909</v>
       </c>
       <c r="D13" t="n">
-        <v>1.572900762131083</v>
+        <v>1.483990117487361</v>
       </c>
       <c r="E13" t="n">
-        <v>10.08686644345704</v>
+        <v>9.51711551011522</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546144835523549</v>
+        <v>0.7545542231037555</v>
       </c>
       <c r="G13" t="n">
-        <v>24.31833720749394</v>
+        <v>22.93416746867874</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71226624340834</v>
+        <v>34.70949426277276</v>
       </c>
       <c r="I13" t="n">
-        <v>2.32119588864189</v>
+        <v>2.245926666234159</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716340522202217</v>
+        <v>4.715963894398474</v>
       </c>
       <c r="K13" t="n">
-        <v>21.51747844911314</v>
+        <v>23.63878785720952</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70868350960299</v>
+        <v>41.63057038130572</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92270300813563</v>
+        <v>99.92520910248433</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.67028448754323</v>
+        <v>83.47641055683982</v>
       </c>
       <c r="C14" t="n">
-        <v>40.41989918776348</v>
+        <v>39.08269332237656</v>
       </c>
       <c r="D14" t="n">
-        <v>1.57484439366167</v>
+        <v>1.485721107823036</v>
       </c>
       <c r="E14" t="n">
-        <v>12.20676645462065</v>
+        <v>11.97063795216786</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555469597383813</v>
+        <v>0.7554343678247639</v>
       </c>
       <c r="G14" t="n">
-        <v>25.93268819928531</v>
+        <v>24.91648764048721</v>
       </c>
       <c r="H14" t="n">
-        <v>36.33946100048184</v>
+        <v>36.70554968567204</v>
       </c>
       <c r="I14" t="n">
-        <v>3.138808981390493</v>
+        <v>2.921115003960135</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722168498364882</v>
+        <v>4.721464798904776</v>
       </c>
       <c r="K14" t="n">
-        <v>15.32971551245675</v>
+        <v>16.52358944316017</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14588746158311</v>
+        <v>44.29646017917216</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89550216180335</v>
+        <v>99.90274294470889</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.98477915305293</v>
+        <v>82.68833222220977</v>
       </c>
       <c r="C15" t="n">
-        <v>40.22028636467547</v>
+        <v>38.74434562705506</v>
       </c>
       <c r="D15" t="n">
-        <v>1.549269511150839</v>
+        <v>1.456455411403552</v>
       </c>
       <c r="E15" t="n">
-        <v>12.44493188494958</v>
+        <v>12.14251862723567</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756332149019833</v>
+        <v>0.7561764039405915</v>
       </c>
       <c r="G15" t="n">
-        <v>25.5115510656383</v>
+        <v>24.42725236715567</v>
       </c>
       <c r="H15" t="n">
-        <v>36.37722616504711</v>
+        <v>36.74317329569674</v>
       </c>
       <c r="I15" t="n">
-        <v>2.618392445873306</v>
+        <v>2.436653592148843</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727075931373955</v>
+        <v>4.726102524628699</v>
       </c>
       <c r="K15" t="n">
-        <v>16.01522084694709</v>
+        <v>17.31166777779022</v>
       </c>
       <c r="L15" t="n">
-        <v>43.67730365000546</v>
+        <v>43.86284451171137</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91281086162802</v>
+        <v>99.91885791655666</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.68611507832944</v>
+        <v>80.16719430022692</v>
       </c>
       <c r="C16" t="n">
-        <v>38.32708615351747</v>
+        <v>36.59968899777331</v>
       </c>
       <c r="D16" t="n">
-        <v>1.460424765827086</v>
+        <v>1.361041573292246</v>
       </c>
       <c r="E16" t="n">
-        <v>12.09525183562814</v>
+        <v>11.68576027387415</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570061855354312</v>
+        <v>0.756815379954775</v>
       </c>
       <c r="G16" t="n">
-        <v>24.04856012640728</v>
+        <v>22.82699884438028</v>
       </c>
       <c r="H16" t="n">
-        <v>36.40964522696745</v>
+        <v>36.77422161497593</v>
       </c>
       <c r="I16" t="n">
-        <v>2.183938278367611</v>
+        <v>2.032260489032193</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731288659596443</v>
+        <v>4.730096124717345</v>
       </c>
       <c r="K16" t="n">
-        <v>18.31388492167057</v>
+        <v>19.83280569977307</v>
       </c>
       <c r="L16" t="n">
-        <v>43.28629580131549</v>
+        <v>43.49982048044947</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92726687650352</v>
+        <v>99.93231517799586</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.21893740392406</v>
+        <v>81.90358201229714</v>
       </c>
       <c r="C17" t="n">
-        <v>39.45230485158514</v>
+        <v>37.86188198189689</v>
       </c>
       <c r="D17" t="n">
-        <v>1.461706776326639</v>
+        <v>1.362163018525129</v>
       </c>
       <c r="E17" t="n">
-        <v>12.83451034323124</v>
+        <v>12.48024249979255</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576707112958756</v>
+        <v>0.7574389663438151</v>
       </c>
       <c r="G17" t="n">
-        <v>24.4330495949213</v>
+        <v>23.29323421296382</v>
       </c>
       <c r="H17" t="n">
-        <v>36.80498567613834</v>
+        <v>37.251948951766</v>
       </c>
       <c r="I17" t="n">
-        <v>2.191572356411437</v>
+        <v>2.024560823256973</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735441945599221</v>
+        <v>4.733993539648846</v>
       </c>
       <c r="K17" t="n">
-        <v>16.78106259607594</v>
+        <v>18.09641798770286</v>
       </c>
       <c r="L17" t="n">
-        <v>43.69364421210449</v>
+        <v>43.9742702291543</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92701165976558</v>
+        <v>99.93257019875405</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.95829641778606</v>
+        <v>79.50519200577627</v>
       </c>
       <c r="C18" t="n">
-        <v>37.53068148913864</v>
+        <v>35.77587769433458</v>
       </c>
       <c r="D18" t="n">
-        <v>1.377422194930886</v>
+        <v>1.275090212561824</v>
       </c>
       <c r="E18" t="n">
-        <v>12.39906402827445</v>
+        <v>11.96386278691774</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582408744448405</v>
+        <v>0.7579751181662897</v>
       </c>
       <c r="G18" t="n">
-        <v>23.02419701882198</v>
+        <v>21.80427346795753</v>
       </c>
       <c r="H18" t="n">
-        <v>36.83268220210649</v>
+        <v>37.27831767744383</v>
       </c>
       <c r="I18" t="n">
-        <v>1.827684633927146</v>
+        <v>1.688328254189744</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739005465280251</v>
+        <v>4.737344488539312</v>
       </c>
       <c r="K18" t="n">
-        <v>19.04170358221395</v>
+        <v>20.49480799422373</v>
       </c>
       <c r="L18" t="n">
-        <v>43.36673791874708</v>
+        <v>43.67307651079565</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93912299009969</v>
+        <v>99.94376219935397</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.03533576606952</v>
+        <v>78.57997333434</v>
       </c>
       <c r="C19" t="n">
-        <v>36.88980855280109</v>
+        <v>35.11047294947123</v>
       </c>
       <c r="D19" t="n">
-        <v>1.343728835319071</v>
+        <v>1.242166359547177</v>
       </c>
       <c r="E19" t="n">
-        <v>12.34977461742819</v>
+        <v>11.88957631132759</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587221565955293</v>
+        <v>0.7584277621293022</v>
       </c>
       <c r="G19" t="n">
-        <v>22.46099820237821</v>
+        <v>21.24126962110978</v>
       </c>
       <c r="H19" t="n">
-        <v>36.85606120092246</v>
+        <v>37.30057936525329</v>
       </c>
       <c r="I19" t="n">
-        <v>1.524037274704005</v>
+        <v>1.407780401664715</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742013478722057</v>
+        <v>4.74017351330814</v>
       </c>
       <c r="K19" t="n">
-        <v>19.96466423393046</v>
+        <v>21.42002666566001</v>
       </c>
       <c r="L19" t="n">
-        <v>43.09475819565936</v>
+        <v>43.42260237780793</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94923098239092</v>
+        <v>99.95310199293917</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.58407864567498</v>
+        <v>75.98000107170611</v>
       </c>
       <c r="C20" t="n">
-        <v>34.67363853503533</v>
+        <v>32.72699284726674</v>
       </c>
       <c r="D20" t="n">
-        <v>1.253308570466604</v>
+        <v>1.148800241203032</v>
       </c>
       <c r="E20" t="n">
-        <v>11.73053878360004</v>
+        <v>11.19153464432889</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591363853938288</v>
+        <v>0.7588183069824529</v>
       </c>
       <c r="G20" t="n">
-        <v>20.94958507129989</v>
+        <v>19.64469209509516</v>
       </c>
       <c r="H20" t="n">
-        <v>36.87618298306445</v>
+        <v>37.31978692860744</v>
       </c>
       <c r="I20" t="n">
-        <v>1.270724443138747</v>
+        <v>1.173754436848808</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744602408711429</v>
+        <v>4.742614418640333</v>
       </c>
       <c r="K20" t="n">
-        <v>22.41592135432502</v>
+        <v>24.01999892829388</v>
       </c>
       <c r="L20" t="n">
-        <v>42.86810574189786</v>
+        <v>43.21390321328203</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95766563125821</v>
+        <v>99.96089498884265</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.99864303656811</v>
+        <v>81.94708325307231</v>
       </c>
       <c r="C21" t="n">
-        <v>37.90199522505104</v>
+        <v>36.44274208604887</v>
       </c>
       <c r="D21" t="n">
-        <v>1.254300759115576</v>
+        <v>1.149584102985041</v>
       </c>
       <c r="E21" t="n">
-        <v>13.51007475153384</v>
+        <v>13.18966885406136</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597373599043029</v>
+        <v>0.7593360720812043</v>
       </c>
       <c r="G21" t="n">
-        <v>22.40788767826343</v>
+        <v>21.36901906210502</v>
       </c>
       <c r="H21" t="n">
-        <v>38.34709396919108</v>
+        <v>39.05617415712879</v>
       </c>
       <c r="I21" t="n">
-        <v>1.971190019157995</v>
+        <v>1.677450554203365</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748358499401893</v>
+        <v>4.745850450507529</v>
       </c>
       <c r="K21" t="n">
-        <v>17.00135696343188</v>
+        <v>18.05291674692769</v>
       </c>
       <c r="L21" t="n">
-        <v>45.03099345318039</v>
+        <v>45.4484642750741</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93434564166331</v>
+        <v>99.94412310805066</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_5_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.66402506540302</v>
+        <v>45.50122151822573</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0080775785875</v>
+        <v>99.45597772499394</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03022919926327</v>
+        <v>88.05201418082055</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90414122156643</v>
+        <v>45.92853424317076</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228756720127899</v>
+        <v>2.22879408759916</v>
       </c>
       <c r="E3" t="n">
-        <v>5.692588119665906</v>
+        <v>5.707655297892606</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429189067092996</v>
+        <v>0.7429313625330534</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96455426569118</v>
+        <v>33.97280490750624</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17426970862778</v>
+        <v>34.17484267652046</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583898311508092</v>
+        <v>6.581664832937432</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643243166933122</v>
+        <v>4.643321015831583</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96977080073672</v>
+        <v>11.94798581917948</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88976255906147</v>
+        <v>48.88723864933846</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636745813646</v>
+        <v>106.7637587116887</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19803503251867</v>
+        <v>87.2173418647687</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71105416649245</v>
+        <v>42.731633455165</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189066779978835</v>
+        <v>2.188993563961704</v>
       </c>
       <c r="E4" t="n">
-        <v>6.507566141939136</v>
+        <v>6.521771579723173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444803533824953</v>
+        <v>0.7444919583056432</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35970981864109</v>
+        <v>33.36613808607348</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24609625559479</v>
+        <v>34.24663008205959</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498113474341737</v>
+        <v>5.496241855234833</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653002208640595</v>
+        <v>4.65307473941027</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80196496748134</v>
+        <v>12.7826581352313</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30409480181765</v>
+        <v>44.30288438646657</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81711393579144</v>
+        <v>99.81717597686286</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.03876416945707</v>
+        <v>86.15355486853741</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4051791023163</v>
+        <v>42.52097511617088</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13251116058632</v>
+        <v>2.137439267566885</v>
       </c>
       <c r="E5" t="n">
-        <v>7.104424740477512</v>
+        <v>7.132895531684428</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458042127921837</v>
+        <v>0.7458136204249187</v>
       </c>
       <c r="G5" t="n">
-        <v>32.49784527033067</v>
+        <v>32.5803122157924</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30699378844045</v>
+        <v>34.30742653954626</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589908666878766</v>
+        <v>4.588332565866784</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661276329951148</v>
+        <v>4.661335127655742</v>
       </c>
       <c r="K5" t="n">
-        <v>13.96123583054294</v>
+        <v>13.84644513146259</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48085969285349</v>
+        <v>43.47990636749888</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727462571274</v>
+        <v>99.84732661513235</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74912441558224</v>
+        <v>84.76424740767564</v>
       </c>
       <c r="C6" t="n">
-        <v>41.82843294515614</v>
+        <v>41.84442158653279</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069728497585069</v>
+        <v>2.069595024509576</v>
       </c>
       <c r="E6" t="n">
-        <v>7.533713166527387</v>
+        <v>7.544719085795133</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469278988807972</v>
+        <v>0.746936733531078</v>
       </c>
       <c r="G6" t="n">
-        <v>31.54108532197334</v>
+        <v>31.54618382936699</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35868334851667</v>
+        <v>34.3590897424296</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830686814093988</v>
+        <v>3.82936840747402</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668299368004983</v>
+        <v>4.668354584569238</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25087558441776</v>
+        <v>15.23575259232437</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79319400745724</v>
+        <v>42.79237213875766</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87250253703114</v>
+        <v>99.87254631761482</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.22519068188669</v>
+        <v>83.19236604030124</v>
       </c>
       <c r="C7" t="n">
-        <v>40.89956098656187</v>
+        <v>40.86741002908867</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995620259283765</v>
+        <v>1.993107528936125</v>
       </c>
       <c r="E7" t="n">
-        <v>7.796683656512167</v>
+        <v>7.798421171467459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747884109699375</v>
+        <v>0.74789300377863</v>
       </c>
       <c r="G7" t="n">
-        <v>30.41173223530044</v>
+        <v>30.38030907250255</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40266904617125</v>
+        <v>34.40307817381699</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196325689298594</v>
+        <v>3.195225816183056</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674275685621095</v>
+        <v>4.674331273616438</v>
       </c>
       <c r="K7" t="n">
-        <v>16.77480931811331</v>
+        <v>16.80763395969876</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21922172826664</v>
+        <v>42.21858466656052</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89359203294183</v>
+        <v>99.89362865534795</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.96399024320075</v>
+        <v>87.90785081242205</v>
       </c>
       <c r="C8" t="n">
-        <v>43.16322386523338</v>
+        <v>43.09318640833068</v>
       </c>
       <c r="D8" t="n">
-        <v>1.99981794518191</v>
+        <v>1.997312478672937</v>
       </c>
       <c r="E8" t="n">
-        <v>9.598766543551612</v>
+        <v>9.576006564025271</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494572459541946</v>
+        <v>0.7494708677140903</v>
       </c>
       <c r="G8" t="n">
-        <v>30.90597378055756</v>
+        <v>30.86131215611312</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47503331389295</v>
+        <v>34.47565991484816</v>
       </c>
       <c r="I8" t="n">
-        <v>5.550833626848803</v>
+        <v>5.563895907835421</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684107787213717</v>
+        <v>4.684192923213065</v>
       </c>
       <c r="K8" t="n">
-        <v>12.03600975679925</v>
+        <v>12.09214918757793</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61612697002624</v>
+        <v>44.62959166355405</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81536059205888</v>
+        <v>99.81492725946266</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.91023841963994</v>
+        <v>85.70655895731144</v>
       </c>
       <c r="C9" t="n">
-        <v>41.97121280652458</v>
+        <v>41.7555735319475</v>
       </c>
       <c r="D9" t="n">
-        <v>1.906611907246875</v>
+        <v>1.897123150648887</v>
       </c>
       <c r="E9" t="n">
-        <v>9.923729606495868</v>
+        <v>9.869813598335488</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508047739941031</v>
+        <v>0.7508248128089426</v>
       </c>
       <c r="G9" t="n">
-        <v>29.46553097847649</v>
+        <v>29.31324486074639</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53701960372874</v>
+        <v>34.53794138921137</v>
       </c>
       <c r="I9" t="n">
-        <v>4.634011712234703</v>
+        <v>4.644956065504489</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692529837463145</v>
+        <v>4.692655080055893</v>
       </c>
       <c r="K9" t="n">
-        <v>14.08976158036006</v>
+        <v>14.29344104268854</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78483579014734</v>
+        <v>43.79643276125741</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84581017703198</v>
+        <v>99.84544733589345</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.63060486955966</v>
+        <v>83.30691531070671</v>
       </c>
       <c r="C10" t="n">
-        <v>40.41065645394345</v>
+        <v>40.07649556281061</v>
       </c>
       <c r="D10" t="n">
-        <v>1.80413914364437</v>
+        <v>1.789076187774274</v>
       </c>
       <c r="E10" t="n">
-        <v>10.03497373560852</v>
+        <v>9.953831066941319</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519621790793874</v>
+        <v>0.751989501432813</v>
       </c>
       <c r="G10" t="n">
-        <v>27.8818765499569</v>
+        <v>27.64376595626927</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59026023765183</v>
+        <v>34.5915170659094</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8676294043725</v>
+        <v>3.876801148424564</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699763619246173</v>
+        <v>4.699934383955082</v>
       </c>
       <c r="K10" t="n">
-        <v>16.36939513044033</v>
+        <v>16.69308468929327</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09122586805415</v>
+        <v>43.101393190521</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87127745243791</v>
+        <v>99.87097344262489</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.25483123154436</v>
+        <v>80.8689859115873</v>
       </c>
       <c r="C11" t="n">
-        <v>38.63434872088116</v>
+        <v>38.23917791724611</v>
       </c>
       <c r="D11" t="n">
-        <v>1.698476503990961</v>
+        <v>1.680575104105382</v>
       </c>
       <c r="E11" t="n">
-        <v>9.985139460525225</v>
+        <v>9.889329326595449</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529577306378904</v>
+        <v>0.7529922210630291</v>
       </c>
       <c r="G11" t="n">
-        <v>26.24892452120824</v>
+        <v>25.9672702410835</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63605560934296</v>
+        <v>34.63764216889935</v>
       </c>
       <c r="I11" t="n">
-        <v>3.227291589352268</v>
+        <v>3.234975468196672</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705985816486817</v>
+        <v>4.706201381643933</v>
       </c>
       <c r="K11" t="n">
-        <v>18.74516876845564</v>
+        <v>19.13101408841268</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51304836054175</v>
+        <v>42.52211907355162</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89256584987855</v>
+        <v>99.89231107921042</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.81142674933471</v>
+        <v>78.41950954383785</v>
       </c>
       <c r="C12" t="n">
-        <v>36.69032867711827</v>
+        <v>36.28999267345856</v>
       </c>
       <c r="D12" t="n">
-        <v>1.590879645801642</v>
+        <v>1.572711872173181</v>
       </c>
       <c r="E12" t="n">
-        <v>9.801335833601637</v>
+        <v>9.704426684456456</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538151857576139</v>
+        <v>0.7538560600472415</v>
       </c>
       <c r="G12" t="n">
-        <v>24.58608031777404</v>
+        <v>24.30063024039688</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67549854485024</v>
+        <v>34.67737876217311</v>
       </c>
       <c r="I12" t="n">
-        <v>2.692472310564457</v>
+        <v>2.69890554929572</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711344910985089</v>
+        <v>4.71160037529526</v>
       </c>
       <c r="K12" t="n">
-        <v>21.18857325066528</v>
+        <v>21.58049045616213</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03145108362333</v>
+        <v>42.03965644070718</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9103530114069</v>
+        <v>99.91013957032787</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.36121214279046</v>
+        <v>75.96163254145203</v>
       </c>
       <c r="C13" t="n">
-        <v>34.65585086396909</v>
+        <v>34.24859584764567</v>
       </c>
       <c r="D13" t="n">
-        <v>1.483990117487361</v>
+        <v>1.465508022967652</v>
       </c>
       <c r="E13" t="n">
-        <v>9.51711551011522</v>
+        <v>9.418143093391864</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545542231037555</v>
+        <v>0.754600806014792</v>
       </c>
       <c r="G13" t="n">
-        <v>22.93416746867874</v>
+        <v>22.64417863855894</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70949426277276</v>
+        <v>34.71163707668043</v>
       </c>
       <c r="I13" t="n">
-        <v>2.245926666234159</v>
+        <v>2.251309866245906</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715963894398474</v>
+        <v>4.716255037592449</v>
       </c>
       <c r="K13" t="n">
-        <v>23.63878785720952</v>
+        <v>24.03836745854796</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63057038130572</v>
+        <v>41.63806709521481</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92520910248433</v>
+        <v>99.92503040140843</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.47641055683982</v>
+        <v>83.02977425626977</v>
       </c>
       <c r="C14" t="n">
-        <v>39.08269332237656</v>
+        <v>38.60127280461151</v>
       </c>
       <c r="D14" t="n">
-        <v>1.485721107823036</v>
+        <v>1.4672697200807</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97063795216786</v>
+        <v>11.84100831749043</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554343678247639</v>
+        <v>0.7555079167508816</v>
       </c>
       <c r="G14" t="n">
-        <v>24.91648764048721</v>
+        <v>24.58388970158343</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70554968567204</v>
+        <v>36.6658545131666</v>
       </c>
       <c r="I14" t="n">
-        <v>2.921115003960135</v>
+        <v>2.99431960750472</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721464798904776</v>
+        <v>4.721924479693009</v>
       </c>
       <c r="K14" t="n">
-        <v>16.52358944316017</v>
+        <v>16.97022574373022</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29646017917216</v>
+        <v>44.32881063707769</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90274294470889</v>
+        <v>99.90030918541942</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.68833222220977</v>
+        <v>82.26682866286843</v>
       </c>
       <c r="C15" t="n">
-        <v>38.74434562705506</v>
+        <v>38.30060778576866</v>
       </c>
       <c r="D15" t="n">
-        <v>1.456455411403552</v>
+        <v>1.439181834534006</v>
       </c>
       <c r="E15" t="n">
-        <v>12.14251862723567</v>
+        <v>12.03063498932442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561764039405915</v>
+        <v>0.7562725430491911</v>
       </c>
       <c r="G15" t="n">
-        <v>24.42725236715567</v>
+        <v>24.11328128461655</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74317329569674</v>
+        <v>36.7029628954736</v>
       </c>
       <c r="I15" t="n">
-        <v>2.436653592148843</v>
+        <v>2.497791721813227</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726102524628699</v>
+        <v>4.726703394057444</v>
       </c>
       <c r="K15" t="n">
-        <v>17.31166777779022</v>
+        <v>17.73317133713154</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86284451171137</v>
+        <v>43.88304533244688</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91885791655666</v>
+        <v>99.9168244553471</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.16719430022692</v>
+        <v>79.82890367629754</v>
       </c>
       <c r="C16" t="n">
-        <v>36.59968899777331</v>
+        <v>36.24836118187178</v>
       </c>
       <c r="D16" t="n">
-        <v>1.361041573292246</v>
+        <v>1.346996316505225</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68576027387415</v>
+        <v>11.60724061811604</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756815379954775</v>
+        <v>0.7569304273451813</v>
       </c>
       <c r="G16" t="n">
-        <v>22.82699884438028</v>
+        <v>22.56872640401951</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77422161497593</v>
+        <v>36.73489093930802</v>
       </c>
       <c r="I16" t="n">
-        <v>2.032260489032193</v>
+        <v>2.083303800096184</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730096124717345</v>
+        <v>4.730815170907383</v>
       </c>
       <c r="K16" t="n">
-        <v>19.83280569977307</v>
+        <v>20.17109632370244</v>
       </c>
       <c r="L16" t="n">
-        <v>43.49982048044947</v>
+        <v>43.51115939104207</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93231517799586</v>
+        <v>99.9306168966163</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.90358201229714</v>
+        <v>81.60629898997415</v>
       </c>
       <c r="C17" t="n">
-        <v>37.86188198189689</v>
+        <v>37.5366753387182</v>
       </c>
       <c r="D17" t="n">
-        <v>1.362163018525129</v>
+        <v>1.348141433420442</v>
       </c>
       <c r="E17" t="n">
-        <v>12.48024249979255</v>
+        <v>12.41947237632406</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574389663438151</v>
+        <v>0.7575739137640932</v>
       </c>
       <c r="G17" t="n">
-        <v>23.29323421296382</v>
+        <v>23.04339852791567</v>
       </c>
       <c r="H17" t="n">
-        <v>37.251948951766</v>
+        <v>37.22160609141022</v>
       </c>
       <c r="I17" t="n">
-        <v>2.024560823256973</v>
+        <v>2.081269686114092</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733993539648846</v>
+        <v>4.734836961025582</v>
       </c>
       <c r="K17" t="n">
-        <v>18.09641798770286</v>
+        <v>18.39370101002584</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9742702291543</v>
+        <v>44.00030692302175</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93257019875405</v>
+        <v>99.93068327176579</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.50519200577627</v>
+        <v>79.34611942525716</v>
       </c>
       <c r="C18" t="n">
-        <v>35.77587769433458</v>
+        <v>35.59747192088977</v>
       </c>
       <c r="D18" t="n">
-        <v>1.275090212561824</v>
+        <v>1.266288798478575</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96386278691774</v>
+        <v>11.95469801834594</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579751181662897</v>
+        <v>0.758126298575411</v>
       </c>
       <c r="G18" t="n">
-        <v>21.80427346795753</v>
+        <v>21.64431469237183</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27831767744383</v>
+        <v>37.24874621527694</v>
       </c>
       <c r="I18" t="n">
-        <v>1.688328254189744</v>
+        <v>1.735656036112128</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737344488539312</v>
+        <v>4.738289366096319</v>
       </c>
       <c r="K18" t="n">
-        <v>20.49480799422373</v>
+        <v>20.65388057474285</v>
       </c>
       <c r="L18" t="n">
-        <v>43.67307651079565</v>
+        <v>43.69083445753088</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94376219935397</v>
+        <v>99.9421869531635</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.57997333434</v>
+        <v>78.5098569133027</v>
       </c>
       <c r="C19" t="n">
-        <v>35.11047294947123</v>
+        <v>35.02822863416619</v>
       </c>
       <c r="D19" t="n">
-        <v>1.242166359547177</v>
+        <v>1.236675637426079</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88957631132759</v>
+        <v>11.91633945363874</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584277621293022</v>
+        <v>0.7585921477382266</v>
       </c>
       <c r="G19" t="n">
-        <v>21.24126962110978</v>
+        <v>21.13814534330533</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30057936525329</v>
+        <v>37.2716346143114</v>
       </c>
       <c r="I19" t="n">
-        <v>1.407780401664715</v>
+        <v>1.447268793519004</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74017351330814</v>
+        <v>4.741200923363915</v>
       </c>
       <c r="K19" t="n">
-        <v>21.42002666566001</v>
+        <v>21.49014308669732</v>
       </c>
       <c r="L19" t="n">
-        <v>43.42260237780793</v>
+        <v>43.43341561146669</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95310199293917</v>
+        <v>99.9517873323302</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.98000107170611</v>
+        <v>76.03060034838299</v>
       </c>
       <c r="C20" t="n">
-        <v>32.72699284726674</v>
+        <v>32.77150557184411</v>
       </c>
       <c r="D20" t="n">
-        <v>1.148800241203032</v>
+        <v>1.147870732205044</v>
       </c>
       <c r="E20" t="n">
-        <v>11.19153464432889</v>
+        <v>11.26175045583279</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588183069824529</v>
+        <v>0.7589934728343369</v>
       </c>
       <c r="G20" t="n">
-        <v>19.64469209509516</v>
+        <v>19.62022832695035</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31978692860744</v>
+        <v>37.29135277562955</v>
       </c>
       <c r="I20" t="n">
-        <v>1.173754436848808</v>
+        <v>1.206695379716311</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742614418640333</v>
+        <v>4.743709205214605</v>
       </c>
       <c r="K20" t="n">
-        <v>24.01999892829388</v>
+        <v>23.969399651617</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21390321328203</v>
+        <v>43.21889286560782</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96089498884265</v>
+        <v>99.95979808906893</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.94708325307231</v>
+        <v>81.87760496804276</v>
       </c>
       <c r="C21" t="n">
-        <v>36.44274208604887</v>
+        <v>36.36922093568796</v>
       </c>
       <c r="D21" t="n">
-        <v>1.149584102985041</v>
+        <v>1.148699274745052</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18966885406136</v>
+        <v>13.20911024958024</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593360720812043</v>
+        <v>0.7595413205685702</v>
       </c>
       <c r="G21" t="n">
-        <v>21.36901906210502</v>
+        <v>21.27812169373745</v>
       </c>
       <c r="H21" t="n">
-        <v>39.05617415712879</v>
+        <v>38.96200130545436</v>
       </c>
       <c r="I21" t="n">
-        <v>1.677450554203365</v>
+        <v>1.772997870403525</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745850450507529</v>
+        <v>4.747133253553563</v>
       </c>
       <c r="K21" t="n">
-        <v>18.05291674692769</v>
+        <v>18.12239503195723</v>
       </c>
       <c r="L21" t="n">
-        <v>45.4484642750741</v>
+        <v>45.44932673138716</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94412310805066</v>
+        <v>99.94094269903235</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_5_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.50122151822573</v>
+        <v>43.36441772451897</v>
       </c>
       <c r="M2" t="n">
-        <v>99.45597772499394</v>
+        <v>96.79631280226806</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05201418082055</v>
+        <v>81.39423717208236</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92853424317076</v>
+        <v>43.14979272763791</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22879408759916</v>
+        <v>2.17547084863515</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707655297892606</v>
+        <v>4.14698510061603</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429313625330534</v>
+        <v>0.737574581270435</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97280490750624</v>
+        <v>32.72270734822037</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17484267652046</v>
+        <v>33.92843073844001</v>
       </c>
       <c r="I3" t="n">
-        <v>6.581664832937432</v>
+        <v>3.073227421960146</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643321015831583</v>
+        <v>4.609841132940218</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94798581917948</v>
+        <v>18.60576282791765</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88723864933846</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637587116887</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.2173418647687</v>
+        <v>88.49530448319342</v>
       </c>
       <c r="C4" t="n">
-        <v>42.731633455165</v>
+        <v>42.78322315589621</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188993563961704</v>
+        <v>2.181174570522739</v>
       </c>
       <c r="E4" t="n">
-        <v>6.521771579723173</v>
+        <v>6.550125728932487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444919583056432</v>
+        <v>0.7395083788598448</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36613808607348</v>
+        <v>33.42458495621064</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24663008205959</v>
+        <v>34.01738542755286</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496241855234833</v>
+        <v>6.960598053240812</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65307473941027</v>
+        <v>4.62192736787403</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7826581352313</v>
+        <v>11.5046955168066</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30288438646657</v>
+        <v>45.48066811904182</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81717597686286</v>
+        <v>99.76858679174462</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.15355486853741</v>
+        <v>87.30655968330912</v>
       </c>
       <c r="C5" t="n">
-        <v>42.52097511617088</v>
+        <v>42.67339856425821</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137439267566885</v>
+        <v>2.124372751217474</v>
       </c>
       <c r="E5" t="n">
-        <v>7.132895531684428</v>
+        <v>7.348443797076099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458136204249187</v>
+        <v>0.7411497361866319</v>
       </c>
       <c r="G5" t="n">
-        <v>32.5803122157924</v>
+        <v>32.55414695427613</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30742653954626</v>
+        <v>34.09288786458507</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588332565866784</v>
+        <v>5.813372728801248</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661335127655742</v>
+        <v>4.63218585116645</v>
       </c>
       <c r="K5" t="n">
-        <v>13.84644513146259</v>
+        <v>12.69344031669088</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47990636749888</v>
+        <v>44.43981117312757</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84732661513235</v>
+        <v>99.80665005407666</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.76424740767564</v>
+        <v>85.80644158925151</v>
       </c>
       <c r="C6" t="n">
-        <v>41.84442158653279</v>
+        <v>42.07540802369888</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069595024509576</v>
+        <v>2.052407510917561</v>
       </c>
       <c r="E6" t="n">
-        <v>7.544719085795133</v>
+        <v>7.908443199735603</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746936733531078</v>
+        <v>0.7425471654087553</v>
       </c>
       <c r="G6" t="n">
-        <v>31.54618382936699</v>
+        <v>31.45134284092996</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3590897424296</v>
+        <v>34.15716960880275</v>
       </c>
       <c r="I6" t="n">
-        <v>3.82936840747402</v>
+        <v>4.85361147965216</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668354584569238</v>
+        <v>4.640919783804721</v>
       </c>
       <c r="K6" t="n">
-        <v>15.23575259232437</v>
+        <v>14.19355841074851</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79237213875766</v>
+        <v>43.56955098975255</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87254631761482</v>
+        <v>99.83851742419994</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.19236604030124</v>
+        <v>84.03072270703854</v>
       </c>
       <c r="C7" t="n">
-        <v>40.86741002908867</v>
+        <v>41.05313454028617</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993107528936125</v>
+        <v>1.967558896848409</v>
       </c>
       <c r="E7" t="n">
-        <v>7.798421171467459</v>
+        <v>8.256696133259309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.74789300377863</v>
+        <v>0.7437404548964425</v>
       </c>
       <c r="G7" t="n">
-        <v>30.38030907250255</v>
+        <v>30.15111233774221</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40307817381699</v>
+        <v>34.21206092523636</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195225816183056</v>
+        <v>4.051176115953035</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674331273616438</v>
+        <v>4.648377843102766</v>
       </c>
       <c r="K7" t="n">
-        <v>16.80763395969876</v>
+        <v>15.96927729296148</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21858466656052</v>
+        <v>42.84276562565093</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89362865534795</v>
+        <v>99.86517745889857</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.90785081242205</v>
+        <v>82.04062950849634</v>
       </c>
       <c r="C8" t="n">
-        <v>43.09318640833068</v>
+        <v>39.69167797364209</v>
       </c>
       <c r="D8" t="n">
-        <v>1.997312478672937</v>
+        <v>1.873147681262219</v>
       </c>
       <c r="E8" t="n">
-        <v>9.576006564025271</v>
+        <v>8.423943571682919</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494708677140903</v>
+        <v>0.7447620226164613</v>
       </c>
       <c r="G8" t="n">
-        <v>30.86131215611312</v>
+        <v>28.7043433634352</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47565991484816</v>
+        <v>34.25905304035722</v>
       </c>
       <c r="I8" t="n">
-        <v>5.563895907835421</v>
+        <v>3.38061718778942</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684192923213065</v>
+        <v>4.654762641352884</v>
       </c>
       <c r="K8" t="n">
-        <v>12.09214918757793</v>
+        <v>17.95937049150368</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62959166355405</v>
+        <v>42.23641886496665</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81492725946266</v>
+        <v>99.88746733011241</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.70655895731144</v>
+        <v>79.91626508495672</v>
       </c>
       <c r="C9" t="n">
-        <v>41.7555735319475</v>
+        <v>38.09136238042796</v>
       </c>
       <c r="D9" t="n">
-        <v>1.897123150648887</v>
+        <v>1.773203038509988</v>
       </c>
       <c r="E9" t="n">
-        <v>9.869813598335488</v>
+        <v>8.444553791332455</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508248128089426</v>
+        <v>0.7456381887420839</v>
       </c>
       <c r="G9" t="n">
-        <v>29.31324486074639</v>
+        <v>27.17277947683192</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53794138921137</v>
+        <v>34.29935668213586</v>
       </c>
       <c r="I9" t="n">
-        <v>4.644956065504489</v>
+        <v>2.820495227766403</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692655080055893</v>
+        <v>4.660238679638026</v>
       </c>
       <c r="K9" t="n">
-        <v>14.29344104268854</v>
+        <v>20.08373491504327</v>
       </c>
       <c r="L9" t="n">
-        <v>43.79643276125741</v>
+        <v>41.73099667153462</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84544733589345</v>
+        <v>99.90609396700584</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.30691531070671</v>
+        <v>85.19519553257285</v>
       </c>
       <c r="C10" t="n">
-        <v>40.07649556281061</v>
+        <v>41.71102778099011</v>
       </c>
       <c r="D10" t="n">
-        <v>1.789076187774274</v>
+        <v>1.775204219094242</v>
       </c>
       <c r="E10" t="n">
-        <v>9.953831066941319</v>
+        <v>10.4838993959137</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751989501432813</v>
+        <v>0.7464796923002116</v>
       </c>
       <c r="G10" t="n">
-        <v>27.64376595626927</v>
+        <v>28.75251821376236</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5915170659094</v>
+        <v>35.88713824756689</v>
       </c>
       <c r="I10" t="n">
-        <v>3.876801148424564</v>
+        <v>2.884457687059146</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699934383955082</v>
+        <v>4.665498076876324</v>
       </c>
       <c r="K10" t="n">
-        <v>16.69308468929327</v>
+        <v>14.80480446742711</v>
       </c>
       <c r="L10" t="n">
-        <v>43.101393190521</v>
+        <v>43.38812754993289</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87097344262489</v>
+        <v>99.90395979835012</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.8689859115873</v>
+        <v>84.68327300967044</v>
       </c>
       <c r="C11" t="n">
-        <v>38.23917791724611</v>
+        <v>41.53201163437479</v>
       </c>
       <c r="D11" t="n">
-        <v>1.680575104105382</v>
+        <v>1.744318160534999</v>
       </c>
       <c r="E11" t="n">
-        <v>9.889329326595449</v>
+        <v>10.77003194146578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529922210630291</v>
+        <v>0.7472027239572809</v>
       </c>
       <c r="G11" t="n">
-        <v>25.9672702410835</v>
+        <v>28.31068623791436</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63764216889935</v>
+        <v>35.98031955012051</v>
       </c>
       <c r="I11" t="n">
-        <v>3.234975468196672</v>
+        <v>2.460697370944487</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706201381643933</v>
+        <v>4.670017024733007</v>
       </c>
       <c r="K11" t="n">
-        <v>19.13101408841268</v>
+        <v>15.31672699032957</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52211907355162</v>
+        <v>43.0693174994945</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89231107921042</v>
+        <v>99.91805612419886</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.41950954383785</v>
+        <v>82.58897935454002</v>
       </c>
       <c r="C12" t="n">
-        <v>36.28999267345856</v>
+        <v>39.81970893248429</v>
       </c>
       <c r="D12" t="n">
-        <v>1.572711872173181</v>
+        <v>1.656206669056393</v>
       </c>
       <c r="E12" t="n">
-        <v>9.704426684456456</v>
+        <v>10.56804730820907</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538560600472415</v>
+        <v>0.7478216398483908</v>
       </c>
       <c r="G12" t="n">
-        <v>24.30063024039688</v>
+        <v>26.88061639994374</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67737876217311</v>
+        <v>36.01012242800464</v>
       </c>
       <c r="I12" t="n">
-        <v>2.69890554929572</v>
+        <v>2.052279660425345</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71160037529526</v>
+        <v>4.673885249052444</v>
       </c>
       <c r="K12" t="n">
-        <v>21.58049045616213</v>
+        <v>17.41102064545999</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03965644070718</v>
+        <v>42.70091771730726</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91013957032787</v>
+        <v>99.93164729525154</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.96163254145203</v>
+        <v>83.8740183770598</v>
       </c>
       <c r="C13" t="n">
-        <v>34.24859584764567</v>
+        <v>40.87621402647179</v>
       </c>
       <c r="D13" t="n">
-        <v>1.465508022967652</v>
+        <v>1.657456160028635</v>
       </c>
       <c r="E13" t="n">
-        <v>9.418143093391864</v>
+        <v>11.24635980527184</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754600806014792</v>
+        <v>0.7483858184652844</v>
       </c>
       <c r="G13" t="n">
-        <v>22.64417863855894</v>
+        <v>27.25485045955407</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71163707668043</v>
+        <v>36.39124405519708</v>
       </c>
       <c r="I13" t="n">
-        <v>2.251309866245906</v>
+        <v>1.898310713134855</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716255037592449</v>
+        <v>4.677411365408028</v>
       </c>
       <c r="K13" t="n">
-        <v>24.03836745854796</v>
+        <v>16.12598162294022</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63806709521481</v>
+        <v>42.9345750288749</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92503040140843</v>
+        <v>99.93677067828689</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.02977425626977</v>
+        <v>81.84112322335294</v>
       </c>
       <c r="C14" t="n">
-        <v>38.60127280461151</v>
+        <v>39.13781135532617</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4672697200807</v>
+        <v>1.574567615867031</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84100831749043</v>
+        <v>10.94775928989445</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555079167508816</v>
+        <v>0.7488683199736755</v>
       </c>
       <c r="G14" t="n">
-        <v>24.58388970158343</v>
+        <v>25.89184917456345</v>
       </c>
       <c r="H14" t="n">
-        <v>36.6658545131666</v>
+        <v>36.41470632521293</v>
       </c>
       <c r="I14" t="n">
-        <v>2.99431960750472</v>
+        <v>1.582945498005933</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721924479693009</v>
+        <v>4.680426999835473</v>
       </c>
       <c r="K14" t="n">
-        <v>16.97022574373022</v>
+        <v>18.15887677664704</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32881063707769</v>
+        <v>42.65058101488416</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90030918541942</v>
+        <v>99.94726914685738</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.26682866286843</v>
+        <v>80.99534757614433</v>
       </c>
       <c r="C15" t="n">
-        <v>38.30060778576866</v>
+        <v>38.51279131387611</v>
       </c>
       <c r="D15" t="n">
-        <v>1.439181834534006</v>
+        <v>1.539539746603368</v>
       </c>
       <c r="E15" t="n">
-        <v>12.03063498932442</v>
+        <v>10.92869891620989</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562725430491911</v>
+        <v>0.7492821435849739</v>
       </c>
       <c r="G15" t="n">
-        <v>24.11328128461655</v>
+        <v>25.31655262338212</v>
       </c>
       <c r="H15" t="n">
-        <v>36.7029628954736</v>
+        <v>36.43552319396976</v>
       </c>
       <c r="I15" t="n">
-        <v>2.497791721813227</v>
+        <v>1.342737554988137</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726703394057444</v>
+        <v>4.683013397406087</v>
       </c>
       <c r="K15" t="n">
-        <v>17.73317133713154</v>
+        <v>19.00465242385567</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88304533244688</v>
+        <v>42.43782306327329</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9168244553471</v>
+        <v>99.95526680100508</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.82890367629754</v>
+        <v>78.50776579069262</v>
       </c>
       <c r="C16" t="n">
-        <v>36.24836118187178</v>
+        <v>36.23298297141035</v>
       </c>
       <c r="D16" t="n">
-        <v>1.346996316505225</v>
+        <v>1.4388669218904</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60724061811604</v>
+        <v>10.400634789683</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569304273451813</v>
+        <v>0.7496382893445763</v>
       </c>
       <c r="G16" t="n">
-        <v>22.56872640401951</v>
+        <v>23.6610650854907</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73489093930802</v>
+        <v>36.45284157956792</v>
       </c>
       <c r="I16" t="n">
-        <v>2.083303800096184</v>
+        <v>1.119479816312428</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730815170907383</v>
+        <v>4.685239308403602</v>
       </c>
       <c r="K16" t="n">
-        <v>20.17109632370244</v>
+        <v>21.49223420930737</v>
       </c>
       <c r="L16" t="n">
-        <v>43.51115939104207</v>
+        <v>42.23748455386595</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9306168966163</v>
+        <v>99.96270173458367</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.60629898997415</v>
+        <v>83.7151617810356</v>
       </c>
       <c r="C17" t="n">
-        <v>37.5366753387182</v>
+        <v>39.67421448099405</v>
       </c>
       <c r="D17" t="n">
-        <v>1.348141433420442</v>
+        <v>1.439585459994914</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41947237632406</v>
+        <v>12.22320198915039</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575739137640932</v>
+        <v>0.7500126420156272</v>
       </c>
       <c r="G17" t="n">
-        <v>23.04339852791567</v>
+        <v>25.28122680920113</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22160609141022</v>
+        <v>38.07939123165142</v>
       </c>
       <c r="I17" t="n">
-        <v>2.081269686114092</v>
+        <v>1.254164636424453</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734836961025582</v>
+        <v>4.687579012597671</v>
       </c>
       <c r="K17" t="n">
-        <v>18.39370101002584</v>
+        <v>16.28483821896439</v>
       </c>
       <c r="L17" t="n">
-        <v>44.00030692302175</v>
+        <v>43.99916267847041</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93068327176579</v>
+        <v>99.95821537842886</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.34611942525716</v>
+        <v>85.4524527009937</v>
       </c>
       <c r="C18" t="n">
-        <v>35.59747192088977</v>
+        <v>40.42524242276514</v>
       </c>
       <c r="D18" t="n">
-        <v>1.266288798478575</v>
+        <v>1.440814812700304</v>
       </c>
       <c r="E18" t="n">
-        <v>11.95469801834594</v>
+        <v>12.84315550705908</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758126298575411</v>
+        <v>0.7506531250547807</v>
       </c>
       <c r="G18" t="n">
-        <v>21.64431469237183</v>
+        <v>25.42514063888707</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24874621527694</v>
+        <v>38.11190962248763</v>
       </c>
       <c r="I18" t="n">
-        <v>1.735656036112128</v>
+        <v>2.189196963212471</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738289366096319</v>
+        <v>4.69158203159238</v>
       </c>
       <c r="K18" t="n">
-        <v>20.65388057474285</v>
+        <v>14.54754729900628</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69083445753088</v>
+        <v>44.95429930939054</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9421869531635</v>
+        <v>99.92708903116196</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.5098569133027</v>
+        <v>82.66423031607052</v>
       </c>
       <c r="C19" t="n">
-        <v>35.02822863416619</v>
+        <v>37.97559683255754</v>
       </c>
       <c r="D19" t="n">
-        <v>1.236675637426079</v>
+        <v>1.340632510978729</v>
       </c>
       <c r="E19" t="n">
-        <v>11.91633945363874</v>
+        <v>12.25442805870855</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585921477382266</v>
+        <v>0.7512057412499072</v>
       </c>
       <c r="G19" t="n">
-        <v>21.13814534330533</v>
+        <v>23.65728741559551</v>
       </c>
       <c r="H19" t="n">
-        <v>37.2716346143114</v>
+        <v>38.13996686728103</v>
       </c>
       <c r="I19" t="n">
-        <v>1.447268793519004</v>
+        <v>1.825673839444879</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741200923363915</v>
+        <v>4.695035882811921</v>
       </c>
       <c r="K19" t="n">
-        <v>21.49014308669732</v>
+        <v>17.33576968392947</v>
       </c>
       <c r="L19" t="n">
-        <v>43.43341561146669</v>
+        <v>44.62782245675707</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9517873323302</v>
+        <v>99.93918897324409</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.03060034838299</v>
+        <v>79.709719505002</v>
       </c>
       <c r="C20" t="n">
-        <v>32.77150557184411</v>
+        <v>35.30260872649818</v>
       </c>
       <c r="D20" t="n">
-        <v>1.147870732205044</v>
+        <v>1.235091765407851</v>
       </c>
       <c r="E20" t="n">
-        <v>11.26175045583279</v>
+        <v>11.54343046491408</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589934728343369</v>
+        <v>0.7516839799369773</v>
       </c>
       <c r="G20" t="n">
-        <v>19.62022832695035</v>
+        <v>21.79487714911337</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29135277562955</v>
+        <v>38.16424784208981</v>
       </c>
       <c r="I20" t="n">
-        <v>1.206695379716311</v>
+        <v>1.522363428933789</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743709205214605</v>
+        <v>4.69802487460611</v>
       </c>
       <c r="K20" t="n">
-        <v>23.969399651617</v>
+        <v>20.290280494998</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21889286560782</v>
+        <v>44.35639761629702</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95979808906893</v>
+        <v>99.9492868377932</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.87760496804276</v>
+        <v>76.7416409406608</v>
       </c>
       <c r="C21" t="n">
-        <v>36.36922093568796</v>
+        <v>32.56844416016077</v>
       </c>
       <c r="D21" t="n">
-        <v>1.148699274745052</v>
+        <v>1.129683347011751</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20911024958024</v>
+        <v>10.76981689720774</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595413205685702</v>
+        <v>0.7520984178093695</v>
       </c>
       <c r="G21" t="n">
-        <v>21.27812169373745</v>
+        <v>19.93480197594056</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96200130545436</v>
+        <v>38.18528954325584</v>
       </c>
       <c r="I21" t="n">
-        <v>1.772997870403525</v>
+        <v>1.269335648126962</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747133253553563</v>
+        <v>4.700615111308561</v>
       </c>
       <c r="K21" t="n">
-        <v>18.12239503195723</v>
+        <v>23.25835905933921</v>
       </c>
       <c r="L21" t="n">
-        <v>45.44932673138716</v>
+        <v>44.13090890747409</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94094269903235</v>
+        <v>99.95771212697406</v>
       </c>
     </row>
   </sheetData>
